--- a/rocps-automation/ROCPS_Automation_Report.xlsx
+++ b/rocps-automation/ROCPS_Automation_Report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236493" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269895" uniqueCount="322">
   <si>
     <t>Date</t>
   </si>
@@ -929,6 +929,63 @@
   </si>
   <si>
     <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
 </sst>
 </file>
@@ -936,7 +993,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="407" x14ac:knownFonts="1">
+  <fonts count="456" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3380,8 +3437,302 @@
       <b val="true"/>
       <color indexed="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="813">
+  <fills count="911">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7443,8 +7794,498 @@
         <fgColor indexed="30"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1622">
+  <borders count="1818">
     <border>
       <left/>
       <right/>
@@ -14757,11 +15598,893 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="813">
+  <cellXfs count="911">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -17197,6 +18920,300 @@
       <alignment wrapText="true" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="406" fillId="812" borderId="1621" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1625" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="814" borderId="1625" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1629" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="816" borderId="1629" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1633" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="818" borderId="1633" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1637" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="820" borderId="1637" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1641" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="822" borderId="1641" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1645" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="824" borderId="1645" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1649" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="826" borderId="1649" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1653" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="828" borderId="1653" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1657" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="830" borderId="1657" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1661" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="832" borderId="1661" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1665" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="834" borderId="1665" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1669" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="836" borderId="1669" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1673" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="838" borderId="1673" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1677" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="840" borderId="1677" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1681" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="842" borderId="1681" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1685" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="844" borderId="1685" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1689" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="846" borderId="1689" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1693" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="848" borderId="1693" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1697" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="850" borderId="1697" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1701" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="852" borderId="1701" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1705" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="854" borderId="1705" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1709" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="856" borderId="1709" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1713" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="858" borderId="1713" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1717" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="860" borderId="1717" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1721" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="862" borderId="1721" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1725" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="864" borderId="1725" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1729" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="866" borderId="1729" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1733" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="868" borderId="1733" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1737" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="870" borderId="1737" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1741" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="872" borderId="1741" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1745" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="874" borderId="1745" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1749" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="876" borderId="1749" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1753" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="878" borderId="1753" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1757" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="880" borderId="1757" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1761" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="882" borderId="1761" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1765" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="884" borderId="1765" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1769" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="886" borderId="1769" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1773" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="888" borderId="1773" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1777" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="890" borderId="1777" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1781" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="892" borderId="1781" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1785" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="894" borderId="1785" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1789" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="896" borderId="1789" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1793" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="898" borderId="1793" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1797" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="900" borderId="1797" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1801" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="902" borderId="1801" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1805" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="904" borderId="1805" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1809" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="906" borderId="1809" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1813" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="908" borderId="1813" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+      <alignment wrapText="true" vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1817" xfId="0" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="910" borderId="1817" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment wrapText="true" vertical="top" horizontal="center"/>
     </xf>
   </cellXfs>
@@ -17548,2207 +19565,2294 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="812">
+      <c r="A1" t="s" s="910">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="812">
+      <c r="B1" t="s" s="910">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="812">
+      <c r="C1" t="s" s="910">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="812">
+      <c r="D1" t="s" s="910">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="812">
+      <c r="E1" t="s" s="910">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="812">
+      <c r="F1" t="s" s="910">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="812">
+      <c r="G1" t="s" s="910">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="812">
+      <c r="H1" t="s" s="910">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="812">
+      <c r="I1" t="s" s="910">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s" s="811">
+      <c r="A2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I3" t="s" s="811">
+      <c r="A3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I4" t="s" s="811">
+      <c r="A4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I5" t="s" s="811">
+      <c r="A5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I6" t="s" s="811">
+      <c r="A6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I7" t="s" s="811">
+      <c r="A7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s" s="811">
+      <c r="A8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I8" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I9" t="s" s="811">
+      <c r="A9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I9" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I10" t="s" s="811">
+      <c r="A10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I10" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H11" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I11" t="s" s="811">
+      <c r="A11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I11" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H12" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I12" t="s" s="811">
+      <c r="A12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I12" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H13" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I13" t="s" s="811">
+      <c r="A13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H13" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I13" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H14" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I14" t="s" s="811">
+      <c r="A14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I14" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H15" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I15" t="s" s="811">
+      <c r="A15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H15" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I15" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H16" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I16" t="s" s="811">
+      <c r="A16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H16" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I16" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H17" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I17" t="s" s="811">
+      <c r="A17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I17" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H18" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I18" t="s" s="811">
+      <c r="A18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I18" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H19" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I19" t="s" s="811">
+      <c r="A19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H19" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I19" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H20" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I20" t="s" s="811">
+      <c r="A20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H20" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I20" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H21" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I21" t="s" s="811">
+      <c r="A21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H21" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I21" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H22" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I22" t="s" s="811">
+      <c r="A22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H22" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I22" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H23" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I23" t="s" s="811">
+      <c r="A23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H23" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I23" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H24" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I24" t="s" s="811">
+      <c r="A24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H24" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I24" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H25" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I25" t="s" s="811">
+      <c r="A25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I25" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H26" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I26" t="s" s="811">
+      <c r="A26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H26" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I26" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H27" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I27" t="s" s="811">
+      <c r="A27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H27" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I27" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H28" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I28" t="s" s="811">
+      <c r="A28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H28" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I28" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H29" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I29" t="s" s="811">
+      <c r="A29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H29" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I29" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H30" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I30" t="s" s="811">
+      <c r="A30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I30" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H31" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I31" t="s" s="811">
+      <c r="A31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H31" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I31" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H32" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I32" t="s" s="811">
+      <c r="A32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H32" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I32" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H33" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I33" t="s" s="811">
+      <c r="A33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H33" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I33" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H34" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I34" t="s" s="811">
+      <c r="A34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I34" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H35" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I35" t="s" s="811">
+      <c r="A35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I35" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H36" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I36" t="s" s="811">
+      <c r="A36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I36" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H37" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I37" t="s" s="811">
+      <c r="A37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I37" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H38" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I38" t="s" s="811">
+      <c r="A38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H38" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I38" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H39" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I39" t="s" s="811">
+      <c r="A39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I39" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H40" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I40" t="s" s="811">
+      <c r="A40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I40" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I41" t="s" s="811">
+      <c r="A41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I41" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H42" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I42" t="s" s="811">
+      <c r="A42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I42" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H43" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I43" t="s" s="811">
+      <c r="A43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H43" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I43" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H44" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I44" t="s" s="811">
+      <c r="A44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H44" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I44" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H45" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I45" t="s" s="811">
+      <c r="A45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H45" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I45" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H46" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I46" t="s" s="811">
+      <c r="A46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H46" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I46" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="C47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="D47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="G47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="H47" t="s" s="811">
-        <v>9</v>
-      </c>
-      <c r="I47" t="s" s="811">
+      <c r="A47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="H47" t="s" s="909">
+        <v>9</v>
+      </c>
+      <c r="I47" t="s" s="909">
         <v>9</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="811">
+      <c r="A48" t="s" s="909">
         <v>10</v>
       </c>
-      <c r="B48" t="s" s="811">
+      <c r="B48" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C48" t="s" s="811">
+      <c r="C48" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D48" t="s" s="811">
+      <c r="D48" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E48" t="s" s="811">
+      <c r="E48" t="s" s="909">
         <v>17</v>
       </c>
-      <c r="F48" t="s" s="811">
+      <c r="F48" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="G48" t="s" s="811">
+      <c r="G48" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H48" t="s" s="811">
+      <c r="H48" t="s" s="909">
         <v>20</v>
       </c>
-      <c r="I48" t="s" s="811">
+      <c r="I48" t="s" s="909">
         <v>14</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="811">
+      <c r="A49" t="s" s="909">
         <v>21</v>
       </c>
-      <c r="B49" t="s" s="811">
+      <c r="B49" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C49" t="s" s="811">
+      <c r="C49" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D49" t="s" s="811">
+      <c r="D49" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E49" t="s" s="811">
+      <c r="E49" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F49" t="s" s="811">
+      <c r="F49" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G49" t="s" s="811">
+      <c r="G49" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H49" t="s" s="811">
+      <c r="H49" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I49" t="s" s="811">
+      <c r="I49" t="s" s="909">
         <v>22</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="811">
+      <c r="A50" t="s" s="909">
         <v>25</v>
       </c>
-      <c r="B50" t="s" s="811">
+      <c r="B50" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C50" t="s" s="811">
+      <c r="C50" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D50" t="s" s="811">
+      <c r="D50" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E50" t="s" s="811">
+      <c r="E50" t="s" s="909">
         <v>27</v>
       </c>
-      <c r="F50" t="s" s="811">
+      <c r="F50" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G50" t="s" s="811">
+      <c r="G50" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H50" t="s" s="811">
+      <c r="H50" t="s" s="909">
         <v>27</v>
       </c>
-      <c r="I50" t="s" s="811">
+      <c r="I50" t="s" s="909">
         <v>26</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s" s="811">
+      <c r="A51" t="s" s="909">
         <v>28</v>
       </c>
-      <c r="B51" t="s" s="811">
+      <c r="B51" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C51" t="s" s="811">
+      <c r="C51" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D51" t="s" s="811">
+      <c r="D51" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E51" t="s" s="811">
+      <c r="E51" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F51" t="s" s="811">
+      <c r="F51" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G51" t="s" s="811">
+      <c r="G51" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H51" t="s" s="811">
+      <c r="H51" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I51" t="s" s="811">
+      <c r="I51" t="s" s="909">
         <v>36</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s" s="811">
+      <c r="A52" t="s" s="909">
         <v>37</v>
       </c>
-      <c r="B52" t="s" s="811">
+      <c r="B52" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C52" t="s" s="811">
+      <c r="C52" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D52" t="s" s="811">
+      <c r="D52" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E52" t="s" s="811">
+      <c r="E52" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F52" t="s" s="811">
+      <c r="F52" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G52" t="s" s="811">
+      <c r="G52" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H52" t="s" s="811">
+      <c r="H52" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I52" t="s" s="811">
+      <c r="I52" t="s" s="909">
         <v>47</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s" s="811">
+      <c r="A53" t="s" s="909">
         <v>48</v>
       </c>
-      <c r="B53" t="s" s="811">
+      <c r="B53" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C53" t="s" s="811">
+      <c r="C53" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D53" t="s" s="811">
+      <c r="D53" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E53" t="s" s="811">
+      <c r="E53" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F53" t="s" s="811">
+      <c r="F53" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G53" t="s" s="811">
+      <c r="G53" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H53" t="s" s="811">
+      <c r="H53" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I53" t="s" s="811">
+      <c r="I53" t="s" s="909">
         <v>72</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s" s="811">
+      <c r="A54" t="s" s="909">
         <v>73</v>
       </c>
-      <c r="B54" t="s" s="811">
+      <c r="B54" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C54" t="s" s="811">
+      <c r="C54" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D54" t="s" s="811">
+      <c r="D54" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E54" t="s" s="811">
+      <c r="E54" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F54" t="s" s="811">
+      <c r="F54" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G54" t="s" s="811">
+      <c r="G54" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H54" t="s" s="811">
+      <c r="H54" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I54" t="s" s="811">
+      <c r="I54" t="s" s="909">
         <v>91</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="811">
+      <c r="A55" t="s" s="909">
         <v>92</v>
       </c>
-      <c r="B55" t="s" s="811">
+      <c r="B55" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C55" t="s" s="811">
+      <c r="C55" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D55" t="s" s="811">
+      <c r="D55" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E55" t="s" s="811">
+      <c r="E55" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F55" t="s" s="811">
+      <c r="F55" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G55" t="s" s="811">
+      <c r="G55" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H55" t="s" s="811">
+      <c r="H55" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I55" t="s" s="811">
+      <c r="I55" t="s" s="909">
         <v>95</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s" s="811">
+      <c r="A56" t="s" s="909">
         <v>96</v>
       </c>
-      <c r="B56" t="s" s="811">
+      <c r="B56" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C56" t="s" s="811">
+      <c r="C56" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D56" t="s" s="811">
+      <c r="D56" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E56" t="s" s="811">
+      <c r="E56" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F56" t="s" s="811">
+      <c r="F56" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G56" t="s" s="811">
+      <c r="G56" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H56" t="s" s="811">
+      <c r="H56" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I56" t="s" s="811">
+      <c r="I56" t="s" s="909">
         <v>111</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="811">
+      <c r="A57" t="s" s="909">
         <v>112</v>
       </c>
-      <c r="B57" t="s" s="811">
+      <c r="B57" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C57" t="s" s="811">
+      <c r="C57" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D57" t="s" s="811">
+      <c r="D57" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E57" t="s" s="811">
+      <c r="E57" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F57" t="s" s="811">
+      <c r="F57" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G57" t="s" s="811">
+      <c r="G57" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H57" t="s" s="811">
+      <c r="H57" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="I57" t="s" s="811">
+      <c r="I57" t="s" s="909">
         <v>114</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s" s="811">
+      <c r="A58" t="s" s="909">
         <v>115</v>
       </c>
-      <c r="B58" t="s" s="811">
+      <c r="B58" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C58" t="s" s="811">
+      <c r="C58" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D58" t="s" s="811">
+      <c r="D58" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E58" t="s" s="811">
+      <c r="E58" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F58" t="s" s="811">
+      <c r="F58" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G58" t="s" s="811">
+      <c r="G58" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H58" t="s" s="811">
+      <c r="H58" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I58" t="s" s="811">
+      <c r="I58" t="s" s="909">
         <v>127</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s" s="811">
+      <c r="A59" t="s" s="909">
         <v>128</v>
       </c>
-      <c r="B59" t="s" s="811">
+      <c r="B59" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C59" t="s" s="811">
+      <c r="C59" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D59" t="s" s="811">
+      <c r="D59" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E59" t="s" s="811">
+      <c r="E59" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F59" t="s" s="811">
+      <c r="F59" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G59" t="s" s="811">
+      <c r="G59" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H59" t="s" s="811">
+      <c r="H59" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I59" t="s" s="811">
+      <c r="I59" t="s" s="909">
         <v>133</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s" s="811">
+      <c r="A60" t="s" s="909">
         <v>134</v>
       </c>
-      <c r="B60" t="s" s="811">
+      <c r="B60" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C60" t="s" s="811">
+      <c r="C60" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D60" t="s" s="811">
+      <c r="D60" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E60" t="s" s="811">
+      <c r="E60" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F60" t="s" s="811">
+      <c r="F60" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G60" t="s" s="811">
+      <c r="G60" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H60" t="s" s="811">
+      <c r="H60" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I60" t="s" s="811">
+      <c r="I60" t="s" s="909">
         <v>135</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s" s="811">
+      <c r="A61" t="s" s="909">
         <v>136</v>
       </c>
-      <c r="B61" t="s" s="811">
+      <c r="B61" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C61" t="s" s="811">
+      <c r="C61" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D61" t="s" s="811">
+      <c r="D61" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E61" t="s" s="811">
+      <c r="E61" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F61" t="s" s="811">
+      <c r="F61" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G61" t="s" s="811">
+      <c r="G61" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H61" t="s" s="811">
+      <c r="H61" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I61" t="s" s="811">
+      <c r="I61" t="s" s="909">
         <v>138</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s" s="811">
+      <c r="A62" t="s" s="909">
         <v>139</v>
       </c>
-      <c r="B62" t="s" s="811">
+      <c r="B62" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C62" t="s" s="811">
+      <c r="C62" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D62" t="s" s="811">
+      <c r="D62" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E62" t="s" s="811">
+      <c r="E62" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F62" t="s" s="811">
+      <c r="F62" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G62" t="s" s="811">
+      <c r="G62" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H62" t="s" s="811">
+      <c r="H62" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I62" t="s" s="811">
+      <c r="I62" t="s" s="909">
         <v>141</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s" s="811">
+      <c r="A63" t="s" s="909">
         <v>142</v>
       </c>
-      <c r="B63" t="s" s="811">
+      <c r="B63" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C63" t="s" s="811">
+      <c r="C63" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D63" t="s" s="811">
+      <c r="D63" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E63" t="s" s="811">
+      <c r="E63" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F63" t="s" s="811">
+      <c r="F63" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="G63" t="s" s="811">
+      <c r="G63" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H63" t="s" s="811">
+      <c r="H63" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I63" t="s" s="811">
+      <c r="I63" t="s" s="909">
         <v>151</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="811">
+      <c r="A64" t="s" s="909">
         <v>152</v>
       </c>
-      <c r="B64" t="s" s="811">
+      <c r="B64" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C64" t="s" s="811">
+      <c r="C64" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D64" t="s" s="811">
+      <c r="D64" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E64" t="s" s="811">
+      <c r="E64" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F64" t="s" s="811">
+      <c r="F64" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G64" t="s" s="811">
+      <c r="G64" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H64" t="s" s="811">
+      <c r="H64" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I64" t="s" s="811">
+      <c r="I64" t="s" s="909">
         <v>158</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="811">
+      <c r="A65" t="s" s="909">
         <v>159</v>
       </c>
-      <c r="B65" t="s" s="811">
+      <c r="B65" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C65" t="s" s="811">
+      <c r="C65" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D65" t="s" s="811">
+      <c r="D65" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E65" t="s" s="811">
+      <c r="E65" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F65" t="s" s="811">
+      <c r="F65" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G65" t="s" s="811">
+      <c r="G65" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H65" t="s" s="811">
+      <c r="H65" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I65" t="s" s="811">
+      <c r="I65" t="s" s="909">
         <v>169</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="811">
+      <c r="A66" t="s" s="909">
         <v>170</v>
       </c>
-      <c r="B66" t="s" s="811">
+      <c r="B66" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C66" t="s" s="811">
+      <c r="C66" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D66" t="s" s="811">
+      <c r="D66" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E66" t="s" s="811">
+      <c r="E66" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F66" t="s" s="811">
+      <c r="F66" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="G66" t="s" s="811">
+      <c r="G66" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H66" t="s" s="811">
+      <c r="H66" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I66" t="s" s="811">
+      <c r="I66" t="s" s="909">
         <v>172</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="811">
+      <c r="A67" t="s" s="909">
         <v>173</v>
       </c>
-      <c r="B67" t="s" s="811">
+      <c r="B67" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C67" t="s" s="811">
+      <c r="C67" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D67" t="s" s="811">
+      <c r="D67" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E67" t="s" s="811">
+      <c r="E67" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F67" t="s" s="811">
+      <c r="F67" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G67" t="s" s="811">
+      <c r="G67" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H67" t="s" s="811">
+      <c r="H67" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I67" t="s" s="811">
+      <c r="I67" t="s" s="909">
         <v>178</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s" s="811">
+      <c r="A68" t="s" s="909">
         <v>179</v>
       </c>
-      <c r="B68" t="s" s="811">
+      <c r="B68" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C68" t="s" s="811">
+      <c r="C68" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D68" t="s" s="811">
+      <c r="D68" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E68" t="s" s="811">
+      <c r="E68" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F68" t="s" s="811">
+      <c r="F68" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="G68" t="s" s="811">
+      <c r="G68" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H68" t="s" s="811">
+      <c r="H68" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I68" t="s" s="811">
+      <c r="I68" t="s" s="909">
         <v>166</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="811">
+      <c r="A69" t="s" s="909">
         <v>191</v>
       </c>
-      <c r="B69" t="s" s="811">
+      <c r="B69" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C69" t="s" s="811">
+      <c r="C69" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D69" t="s" s="811">
+      <c r="D69" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E69" t="s" s="811">
+      <c r="E69" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F69" t="s" s="811">
+      <c r="F69" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="G69" t="s" s="811">
+      <c r="G69" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H69" t="s" s="811">
+      <c r="H69" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I69" t="s" s="811">
+      <c r="I69" t="s" s="909">
         <v>135</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s" s="811">
+      <c r="A70" t="s" s="909">
         <v>210</v>
       </c>
-      <c r="B70" t="s" s="811">
+      <c r="B70" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C70" t="s" s="811">
+      <c r="C70" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D70" t="s" s="811">
+      <c r="D70" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E70" t="s" s="811">
+      <c r="E70" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F70" t="s" s="811">
+      <c r="F70" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="G70" t="s" s="811">
+      <c r="G70" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H70" t="s" s="811">
+      <c r="H70" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I70" t="s" s="811">
+      <c r="I70" t="s" s="909">
         <v>106</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="811">
+      <c r="A71" t="s" s="909">
         <v>220</v>
       </c>
-      <c r="B71" t="s" s="811">
+      <c r="B71" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C71" t="s" s="811">
+      <c r="C71" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D71" t="s" s="811">
+      <c r="D71" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E71" t="s" s="811">
+      <c r="E71" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F71" t="s" s="811">
+      <c r="F71" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="G71" t="s" s="811">
+      <c r="G71" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="H71" t="s" s="811">
+      <c r="H71" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I71" t="s" s="811">
+      <c r="I71" t="s" s="909">
         <v>235</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="811">
+      <c r="A72" t="s" s="909">
         <v>236</v>
       </c>
-      <c r="B72" t="s" s="811">
+      <c r="B72" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C72" t="s" s="811">
+      <c r="C72" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D72" t="s" s="811">
+      <c r="D72" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E72" t="s" s="811">
+      <c r="E72" t="s" s="909">
         <v>246</v>
       </c>
-      <c r="F72" t="s" s="811">
+      <c r="F72" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G72" t="s" s="811">
+      <c r="G72" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H72" t="s" s="811">
+      <c r="H72" t="s" s="909">
         <v>247</v>
       </c>
-      <c r="I72" t="s" s="811">
+      <c r="I72" t="s" s="909">
         <v>245</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="811">
+      <c r="A73" t="s" s="909">
         <v>248</v>
       </c>
-      <c r="B73" t="s" s="811">
+      <c r="B73" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C73" t="s" s="811">
+      <c r="C73" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D73" t="s" s="811">
+      <c r="D73" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E73" t="s" s="811">
+      <c r="E73" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F73" t="s" s="811">
+      <c r="F73" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G73" t="s" s="811">
+      <c r="G73" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H73" t="s" s="811">
+      <c r="H73" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I73" t="s" s="811">
+      <c r="I73" t="s" s="909">
         <v>272</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s" s="811">
+      <c r="A74" t="s" s="909">
         <v>273</v>
       </c>
-      <c r="B74" t="s" s="811">
+      <c r="B74" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C74" t="s" s="811">
+      <c r="C74" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D74" t="s" s="811">
+      <c r="D74" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E74" t="s" s="811">
+      <c r="E74" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="F74" t="s" s="811">
+      <c r="F74" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G74" t="s" s="811">
+      <c r="G74" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H74" t="s" s="811">
+      <c r="H74" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="I74" t="s" s="811">
+      <c r="I74" t="s" s="909">
         <v>287</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="811">
+      <c r="A75" t="s" s="909">
         <v>288</v>
       </c>
-      <c r="B75" t="s" s="811">
+      <c r="B75" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C75" t="s" s="811">
+      <c r="C75" t="s" s="909">
         <v>15</v>
       </c>
-      <c r="D75" t="s" s="811">
+      <c r="D75" t="s" s="909">
         <v>16</v>
       </c>
-      <c r="E75" t="s" s="811">
+      <c r="E75" t="s" s="909">
         <v>23</v>
       </c>
-      <c r="F75" t="s" s="811">
+      <c r="F75" t="s" s="909">
         <v>24</v>
       </c>
-      <c r="G75" t="s" s="811">
+      <c r="G75" t="s" s="909">
         <v>19</v>
       </c>
-      <c r="H75" t="s" s="811">
+      <c r="H75" t="s" s="909">
         <v>18</v>
       </c>
-      <c r="I75" t="s" s="811">
+      <c r="I75" t="s" s="909">
         <v>301</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="811">
+      <c r="A76" t="s" s="909">
         <v>302</v>
       </c>
-      <c r="B76" t="s" s="811">
+      <c r="B76" t="s" s="909">
         <v>11</v>
       </c>
-      <c r="C76" t="n" s="811">
+      <c r="C76" t="s" s="909">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s" s="909">
+        <v>16</v>
+      </c>
+      <c r="E76" t="s" s="909">
+        <v>19</v>
+      </c>
+      <c r="F76" t="s" s="909">
+        <v>24</v>
+      </c>
+      <c r="G76" t="s" s="909">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s" s="909">
+        <v>24</v>
+      </c>
+      <c r="I76" t="s" s="909">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="909">
+        <v>313</v>
+      </c>
+      <c r="B77" t="s" s="909">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s" s="909">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s" s="909">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s" s="909">
+        <v>19</v>
+      </c>
+      <c r="F77" t="s" s="909">
+        <v>19</v>
+      </c>
+      <c r="G77" t="s" s="909">
+        <v>24</v>
+      </c>
+      <c r="H77" t="s" s="909">
+        <v>24</v>
+      </c>
+      <c r="I77" t="s" s="909">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="909">
+        <v>316</v>
+      </c>
+      <c r="B78" t="s" s="909">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s" s="909">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s" s="909">
+        <v>16</v>
+      </c>
+      <c r="E78" t="s" s="909">
+        <v>18</v>
+      </c>
+      <c r="F78" t="s" s="909">
+        <v>19</v>
+      </c>
+      <c r="G78" t="s" s="909">
+        <v>24</v>
+      </c>
+      <c r="H78" t="s" s="909">
+        <v>19</v>
+      </c>
+      <c r="I78" t="s" s="909">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="909">
+        <v>319</v>
+      </c>
+      <c r="B79" t="s" s="909">
+        <v>11</v>
+      </c>
+      <c r="C79" t="n" s="909">
         <v>1500.0</v>
       </c>
-      <c r="D76" t="n" s="811">
+      <c r="D79" t="n" s="909">
         <v>1200.0</v>
       </c>
-      <c r="E76" t="n" s="811">
+      <c r="E79" t="n" s="909">
+        <v>3.0</v>
+      </c>
+      <c r="F79" t="n" s="909">
+        <v>0.0</v>
+      </c>
+      <c r="G79" t="n" s="909">
         <v>1.0</v>
       </c>
-      <c r="F76" t="n" s="811">
-        <v>1.0</v>
-      </c>
-      <c r="G76" t="n" s="811">
-        <v>0.0</v>
-      </c>
-      <c r="H76" t="n" s="811">
-        <v>0.0</v>
-      </c>
-      <c r="I76" t="s" s="811">
-        <v>233</v>
+      <c r="H79" t="n" s="909">
+        <v>2.0</v>
+      </c>
+      <c r="I79" t="s" s="909">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
